--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-22228</t>
+          <t>I-132498</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.371005</t>
+          <t>-8.3536904</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-74.560688</t>
+          <t>-74.5835364</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>JR. Iparia con JR . Garcilaso de la Vega</t>
+          <t>Orellana / Purús</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-22440</t>
+          <t>I-21423</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-8.36004</t>
+          <t>-8.3716871</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-74.574254</t>
+          <t>-74.5570996</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>JR. Callería con JR. Nueva Luz de Fátima</t>
+          <t>Avenida Miraflores / Avenida Túpac Amaru</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-132498</t>
+          <t>I-21645</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-8.3536904</t>
+          <t>-8.380552</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-74.5835364</t>
+          <t>-74.5691333</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Orellana / Purús</t>
+          <t>Arbonización / Balta</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-21423</t>
+          <t>I-22228</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,22 +664,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-8.3716871</t>
+          <t>-8.371005</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-74.5570996</t>
+          <t>-74.560688</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Miraflores / Avenida Túpac Amaru</t>
+          <t>Calle Iparía / Calle Gacilazo de la Vega</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-21428</t>
+          <t>I-22440</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-8.3715873</t>
+          <t>-8.36004</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-74.557136</t>
+          <t>-74.574254</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Miraflores / Avenida Túpac Amaru</t>
+          <t>Jirón Callería / Calle Nueva Luz de Fátima</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-21639</t>
+          <t>I-22447</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-8.380893</t>
+          <t>-8.3569986</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-74.5691872</t>
+          <t>-74.5772759</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Arbonización</t>
+          <t>2 de Mayo / Jirón Callería</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-21645</t>
+          <t>I-23211</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.380552</t>
+          <t>-8.3729837</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-74.5691333</t>
+          <t>-74.5996841</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Arbonización / Balta</t>
+          <t>2 de Mayo / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-21646</t>
+          <t>I-252662</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.3805423</t>
+          <t>-8.3745276</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-74.5690656</t>
+          <t>-74.5653321</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Arbonización / Balta</t>
+          <t>Antigua Carretera a Yarinacocha / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -891,266 +891,6 @@
         </is>
       </c>
       <c r="J9" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>l-22447</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-8.3569986</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-74.5772759</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2 de Mayo / Jr. Callería</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>l-23211</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-8.3729837</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-74.5996841</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2 de Mayo</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>l-252661</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-8.3746587</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-74.5657043</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>l-252662</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-8.3745276</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-74.5653321</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Antigua Carretera a Yarinacocha</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>l-774381</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-8.3742818</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-74.5656024</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Antigua Carretera a Yarinacocha</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
         <is>
           <t>250105</t>
         </is>

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Calle Iparía / Calle Gacilazo de la Vega</t>
+          <t>Gacilazo de la Vega / Iparía</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jirón Callería / Calle Nueva Luz de Fátima</t>
+          <t>Jirón Callería / Nueva Luz de Fátima</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>250105</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>YARINACOCHA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-132498</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-8.3536904</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>250105</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>250105</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>YARINACOCHA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-21423</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-8.3716871</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>250105</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>250105</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>YARINACOCHA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-21645</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-8.380552</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>250105</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>250105</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>YARINACOCHA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-22228</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-8.371005</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>250105</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>250105</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>YARINACOCHA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-22440</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-8.36004</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>250105</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>250105</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>YARINACOCHA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-22447</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-8.3569986</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>250105</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>250105</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>YARINACOCHA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-23211</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-8.3729837</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>250105</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>250105</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>YARINACOCHA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-252662</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>250105</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>YARINACOCHA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-8.3745276</t>
@@ -888,11 +848,6 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>250105</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,51 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>
@@ -848,6 +836,53 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>250105</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>YARINACOCHA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>I-21835</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-8.368717</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-74.561549</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Av. Yarinacocha con Jr. Ramon Castilla</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-YARINACOCHA.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-132498</t>
+          <t>I-252662</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.3536904</t>
+          <t>-8.3745276</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-74.5835364</t>
+          <t>-74.5653321</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Orellana / Purús</t>
+          <t>Antigua Carretera a Yarinacocha / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,22 +533,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-21423</t>
+          <t>I-23211</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-8.3716871</t>
+          <t>-8.3729837</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-74.5570996</t>
+          <t>-74.5996841</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Miraflores / Avenida Túpac Amaru</t>
+          <t>2 de Mayo / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-21645</t>
+          <t>I-22447</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-8.380552</t>
+          <t>-8.3569986</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-74.5691333</t>
+          <t>-74.5772759</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Arbonización / Balta</t>
+          <t>2 de Mayo / Jirón Callería</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-22228</t>
+          <t>I-22440</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-8.371005</t>
+          <t>-8.36004</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-74.560688</t>
+          <t>-74.574254</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Gacilazo de la Vega / Iparía</t>
+          <t>Jirón Callería / Calle Nueva Luz de Fátima</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-22440</t>
+          <t>I-22228</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-8.36004</t>
+          <t>-8.371005</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-74.574254</t>
+          <t>-74.560688</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jirón Callería / Nueva Luz de Fátima</t>
+          <t>Calle Iparía / Calle Gacilazo de la Vega</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,27 +721,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-22447</t>
+          <t>I-21835</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-8.3569986</t>
+          <t>-8.368717</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-74.5772759</t>
+          <t>-74.561549</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2 de Mayo / Jirón Callería</t>
+          <t>Av. Yarinacocha con Jr. Ramon Castilla</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-23211</t>
+          <t>I-21645</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.3729837</t>
+          <t>-8.380552</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-74.5996841</t>
+          <t>-74.5691333</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2 de Mayo / Calle s / n</t>
+          <t>Arbonización / Balta</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-252662</t>
+          <t>I-21423</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.3745276</t>
+          <t>-8.3716871</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-74.5653321</t>
+          <t>-74.5570996</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Antigua Carretera a Yarinacocha / Calle s / n</t>
+          <t>Avenida Miraflores / Avenida Túpac Amaru</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,27 +862,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-21835</t>
+          <t>I-132498</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-8.368717</t>
+          <t>-8.3536904</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-74.561549</t>
+          <t>-74.5835364</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Av. Yarinacocha con Jr. Ramon Castilla</t>
+          <t>Orellana / Purús</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
